--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,126 +628,1029 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Luxembourg National Division</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Differdange 03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>45938.625</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="3" t="n">
+        <v>45938.79166666666</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>45938.79166666666</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK5" s="3" t="n">
+        <v>45938.8125</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>45938.875</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="n">
+        <v>45938.875</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>45938.89583333334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Toronto</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L9" t="n">
         <v>1.53</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M9" t="n">
         <v>4.2</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N9" t="n">
         <v>5.4</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z9" t="n">
         <v>2.08</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="n">
         <v>45938.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="N6" t="n">
-        <v>2.57</v>
+        <v>5.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45938.875</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.57</v>
+        <v>2.57</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1353,44 +1353,44 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45938.875</v>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.57</v>
+        <v>2.57</v>
       </c>
       <c r="M6" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N6" t="n">
-        <v>5.2</v>
+        <v>2.57</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,44 +1224,44 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45938.875</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="M7" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>2.57</v>
+        <v>5.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45938.875</v>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.57</v>
+        <v>5.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45938.875</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.57</v>
+        <v>2.57</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2</v>
+        <v>2.57</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1353,44 +1353,44 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45938.875</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -665,26 +665,26 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45938.625</v>
+        <v>45938.79166666666</v>
       </c>
     </row>
     <row r="3">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,34 +927,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>6.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -978,10 +978,10 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45938.79166666666</v>
+        <v>45938.8125</v>
       </c>
     </row>
     <row r="5">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,34 +1056,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>2.57</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2</v>
+        <v>2.94</v>
       </c>
       <c r="N5" t="n">
-        <v>6.55</v>
+        <v>2.57</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1129,13 +1129,13 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45938.8125</v>
+        <v>45938.875</v>
       </c>
     </row>
     <row r="6">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.57</v>
+        <v>1.9</v>
       </c>
       <c r="M7" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45938.875</v>
+        <v>45938.89583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,11 +1482,11 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
@@ -1522,135 +1522,6 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45938.89583333334</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45938</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Toronto</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3" t="n">
         <v>45938.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,34 +1056,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>2.57</v>
+        <v>5.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45938.875</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.57</v>
+        <v>2.57</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>2.94</v>
       </c>
       <c r="N6" t="n">
-        <v>5.8</v>
+        <v>2.57</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45938.875</v>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,34 +1056,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>2.57</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>2.94</v>
       </c>
       <c r="N5" t="n">
-        <v>5.8</v>
+        <v>2.57</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45938.875</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.57</v>
+        <v>5.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45938.875</v>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK8"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45938.79166666666</v>
+        <v>45938.625</v>
       </c>
     </row>
     <row r="3">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,34 +927,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>6.55</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -978,10 +978,10 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45938.8125</v>
+        <v>45938.79166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
       <c r="N5" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45938.875</v>
+        <v>45938.79166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.57</v>
+        <v>5.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45938.875</v>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45938.89583333334</v>
+        <v>45938.875</v>
       </c>
     </row>
     <row r="8">
@@ -1402,126 +1402,255 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>45938.89583333334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Toronto</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>1.45</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" t="n">
         <v>4.6</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N9" t="n">
         <v>6.6</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="O9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z9" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AA9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3" t="n">
+      <c r="AG9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="n">
         <v>45938.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45938.625</v>
+        <v>45938.79166666666</v>
       </c>
     </row>
     <row r="3">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Y4" t="n">
         <v>2.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45938.79166666666</v>
+        <v>45938.8125</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45938.79166666666</v>
+        <v>45938.875</v>
       </c>
     </row>
     <row r="6">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="Z6" t="n">
         <v>1.7</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45938.875</v>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45938.875</v>
+        <v>45938.89583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,135 +1522,6 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45938.89583333334</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45938</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Toronto</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3" t="n">
         <v>45938.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.18</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45938.79166666666</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>2.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45938.8125</v>
+        <v>45938.79166666666</v>
       </c>
     </row>
     <row r="5">

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,34 +1056,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="Z5" t="n">
         <v>1.7</v>
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45938.875</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.21</v>
+        <v>1.57</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="Z6" t="n">
         <v>1.7</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45938.875</v>

--- a/jogos_2025-10-08.xlsx
+++ b/jogos_2025-10-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,34 +1056,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.21</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="Z5" t="n">
         <v>1.7</v>
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45938.875</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="Z6" t="n">
         <v>1.7</v>
@@ -1236,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45938.875</v>
